--- a/ASIGNATURAS/SSII/TEORIA/Tablas_ASCII_Y_EBCDIC.xlsx
+++ b/ASIGNATURAS/SSII/TEORIA/Tablas_ASCII_Y_EBCDIC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CursoFP\ASIGNATURAS\SSII\TAREAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CursoFP\ASIGNATURAS\SSII\TEORIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4AF3F3-313B-40EF-B434-3A05407DCDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C7E43B-DC72-4BA1-A799-E705D8FF1A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3DD04FD7-2E28-4B73-B8DD-E110BACB8641}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="106">
   <si>
     <t>x0</t>
   </si>
@@ -157,6 +157,204 @@
   </si>
   <si>
     <t>TABLA ASCII</t>
+  </si>
+  <si>
+    <t>SOH</t>
+  </si>
+  <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>ETX</t>
+  </si>
+  <si>
+    <t>EOT</t>
+  </si>
+  <si>
+    <t>ENQ</t>
+  </si>
+  <si>
+    <t>ACK</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>BS</t>
+  </si>
+  <si>
+    <t>HT</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>VT</t>
+  </si>
+  <si>
+    <t>FF</t>
+  </si>
+  <si>
+    <t>CR</t>
+  </si>
+  <si>
+    <t>SO</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>DC1</t>
+  </si>
+  <si>
+    <t>DC2</t>
+  </si>
+  <si>
+    <t>DC3</t>
+  </si>
+  <si>
+    <t>DC4</t>
+  </si>
+  <si>
+    <t>NAK</t>
+  </si>
+  <si>
+    <t>SYN</t>
+  </si>
+  <si>
+    <t>DLE</t>
+  </si>
+  <si>
+    <t>ETB</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>EM</t>
+  </si>
+  <si>
+    <t>SUB</t>
+  </si>
+  <si>
+    <t>ESC</t>
+  </si>
+  <si>
+    <t>FS</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>RS</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>SHY</t>
+  </si>
+  <si>
+    <t>NUL</t>
+  </si>
+  <si>
+    <t>DS</t>
+  </si>
+  <si>
+    <t>SOS</t>
+  </si>
+  <si>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>WUS</t>
+  </si>
+  <si>
+    <t>SEL</t>
+  </si>
+  <si>
+    <t>RNL</t>
+  </si>
+  <si>
+    <t>GE</t>
+  </si>
+  <si>
+    <t>SPS</t>
+  </si>
+  <si>
+    <t>RPT</t>
+  </si>
+  <si>
+    <t>CU3</t>
+  </si>
+  <si>
+    <t>RFF</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>SBS</t>
+  </si>
+  <si>
+    <t>NBS</t>
+  </si>
+  <si>
+    <t>TRN</t>
+  </si>
+  <si>
+    <t>PP</t>
+  </si>
+  <si>
+    <t>NL</t>
+  </si>
+  <si>
+    <t>POC</t>
+  </si>
+  <si>
+    <t>UBS</t>
+  </si>
+  <si>
+    <t>CU1</t>
+  </si>
+  <si>
+    <t>CSP</t>
+  </si>
+  <si>
+    <t>MFA</t>
+  </si>
+  <si>
+    <t>IRS</t>
+  </si>
+  <si>
+    <t>IGS</t>
+  </si>
+  <si>
+    <t>IFS</t>
+  </si>
+  <si>
+    <t>SFE</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>EO</t>
+  </si>
+  <si>
+    <t>ENP</t>
+  </si>
+  <si>
+    <t>INP</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>IUS / ITB</t>
   </si>
 </sst>
 </file>
@@ -186,7 +384,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -247,6 +445,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="30">
     <border>
@@ -657,7 +861,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -827,9 +1031,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -849,6 +1050,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -871,10 +1096,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1181,47 +1402,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
     </row>
     <row r="2" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63"/>
-      <c r="L2" s="63"/>
-      <c r="M2" s="63"/>
-      <c r="N2" s="63"/>
-      <c r="O2" s="63"/>
-      <c r="P2" s="63"/>
-      <c r="Q2" s="63"/>
-      <c r="R2" s="64"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="62" t="s">
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="63"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="W2" s="63"/>
-      <c r="X2" s="63"/>
-      <c r="Y2" s="63"/>
-      <c r="Z2" s="63"/>
-      <c r="AA2" s="63"/>
-      <c r="AB2" s="63"/>
-      <c r="AC2" s="63"/>
-      <c r="AD2" s="63"/>
-      <c r="AE2" s="63"/>
-      <c r="AF2" s="63"/>
-      <c r="AG2" s="63"/>
-      <c r="AH2" s="63"/>
-      <c r="AI2" s="63"/>
-      <c r="AJ2" s="63"/>
-      <c r="AK2" s="64"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="62"/>
+      <c r="Y2" s="62"/>
+      <c r="Z2" s="62"/>
+      <c r="AA2" s="62"/>
+      <c r="AB2" s="62"/>
+      <c r="AC2" s="62"/>
+      <c r="AD2" s="62"/>
+      <c r="AE2" s="62"/>
+      <c r="AF2" s="62"/>
+      <c r="AG2" s="62"/>
+      <c r="AH2" s="62"/>
+      <c r="AI2" s="62"/>
+      <c r="AJ2" s="62"/>
+      <c r="AK2" s="63"/>
     </row>
     <row r="3" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
@@ -1327,421 +1548,510 @@
       <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="9" t="e">
-        <f t="shared" ref="C4:R4" si="0">CHAR(16*$B104 + C$103)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>_x0001_</v>
-      </c>
-      <c r="E4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>_x0002_</v>
-      </c>
-      <c r="F4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>_x0003_</v>
-      </c>
-      <c r="G4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>_x0004_</v>
-      </c>
-      <c r="H4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>_x0005_</v>
-      </c>
-      <c r="I4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>_x0006_</v>
-      </c>
-      <c r="J4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>_x0007_</v>
-      </c>
-      <c r="K4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>_x0008_</v>
-      </c>
-      <c r="L4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">	</v>
-      </c>
-      <c r="M4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">
-</v>
-      </c>
-      <c r="N4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>_x000B_</v>
-      </c>
-      <c r="O4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>_x000C_</v>
-      </c>
-      <c r="P4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>_x000D_</v>
-      </c>
-      <c r="Q4" s="27" t="str">
-        <f t="shared" si="0"/>
-        <v>_x000E_</v>
-      </c>
-      <c r="R4" s="28" t="str">
-        <f t="shared" si="0"/>
-        <v>_x000F_</v>
+      <c r="C4" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="L4" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="N4" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="P4" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q4" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="R4" s="28" t="s">
+        <v>54</v>
       </c>
       <c r="U4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V4" s="9"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="10"/>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10"/>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="10"/>
-      <c r="AE4" s="10"/>
-      <c r="AF4" s="10"/>
-      <c r="AG4" s="10"/>
-      <c r="AH4" s="10"/>
-      <c r="AI4" s="10"/>
-      <c r="AJ4" s="10"/>
-      <c r="AK4" s="11"/>
+      <c r="V4" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="W4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y4" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z4" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB4" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC4" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD4" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE4" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF4" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH4" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI4" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ4" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK4" s="11" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="5" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="25" t="str">
-        <f t="shared" ref="C5:R5" si="1">CHAR(16*$B105 + C$103)</f>
-        <v>_x0010_</v>
-      </c>
-      <c r="D5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>_x0011_</v>
-      </c>
-      <c r="E5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>_x0012_</v>
-      </c>
-      <c r="F5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>_x0013_</v>
-      </c>
-      <c r="G5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>_x0014_</v>
-      </c>
-      <c r="H5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>_x0015_</v>
-      </c>
-      <c r="I5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>_x0016_</v>
-      </c>
-      <c r="J5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>_x0017_</v>
-      </c>
-      <c r="K5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>_x0018_</v>
-      </c>
-      <c r="L5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>_x0019_</v>
-      </c>
-      <c r="M5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>_x001A_</v>
-      </c>
-      <c r="N5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>_x001B_</v>
-      </c>
-      <c r="O5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>_x001C_</v>
-      </c>
-      <c r="P5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>_x001D_</v>
-      </c>
-      <c r="Q5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>_x001E_</v>
-      </c>
-      <c r="R5" s="29" t="str">
-        <f t="shared" si="1"/>
-        <v>_x001F_</v>
+      <c r="C5" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="K5" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="M5" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="N5" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="O5" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="P5" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q5" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="R5" s="29" t="s">
+        <v>71</v>
       </c>
       <c r="U5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="V5" s="12"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="13"/>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="13"/>
-      <c r="AC5" s="13"/>
-      <c r="AD5" s="13"/>
-      <c r="AE5" s="13"/>
-      <c r="AF5" s="13"/>
-      <c r="AG5" s="13"/>
-      <c r="AH5" s="13"/>
-      <c r="AI5" s="13"/>
-      <c r="AJ5" s="13"/>
-      <c r="AK5" s="14"/>
+      <c r="V5" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="W5" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="X5" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y5" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z5" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA5" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB5" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC5" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD5" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE5" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG5" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH5" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI5" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ5" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK5" s="67" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="6" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="30" t="str">
-        <f t="shared" ref="C6:R6" si="2">CHAR(16*$B106 + C$103)</f>
+        <f t="shared" ref="C6:R6" si="0">CHAR(16*$B106 + C$103)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="D6" s="31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>!</v>
       </c>
       <c r="E6" s="31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>"</v>
       </c>
       <c r="F6" s="31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>#</v>
       </c>
       <c r="G6" s="31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>$</v>
       </c>
       <c r="H6" s="31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>%</v>
       </c>
       <c r="I6" s="31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>&amp;</v>
       </c>
       <c r="J6" s="31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>'</v>
       </c>
       <c r="K6" s="31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>(</v>
       </c>
       <c r="L6" s="31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>)</v>
       </c>
       <c r="M6" s="31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>*</v>
       </c>
       <c r="N6" s="31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>+</v>
       </c>
       <c r="O6" s="31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>,</v>
       </c>
       <c r="P6" s="31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="Q6" s="31" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>.</v>
       </c>
       <c r="R6" s="32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>/</v>
       </c>
       <c r="U6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="V6" s="12"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="13"/>
-      <c r="AD6" s="13"/>
-      <c r="AE6" s="13"/>
-      <c r="AF6" s="13"/>
-      <c r="AG6" s="13"/>
-      <c r="AH6" s="13"/>
-      <c r="AI6" s="13"/>
-      <c r="AJ6" s="13"/>
-      <c r="AK6" s="14"/>
+      <c r="V6" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="W6" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="X6" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y6" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z6" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA6" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB6" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC6" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD6" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE6" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF6" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="AG6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH6" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI6" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ6" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK6" s="14" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="7" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="30" t="str">
-        <f t="shared" ref="C7:R7" si="3">CHAR(16*$B107 + C$103)</f>
+        <f t="shared" ref="C7:R7" si="1">CHAR(16*$B107 + C$103)</f>
         <v>0</v>
       </c>
       <c r="D7" s="31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E7" s="31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="F7" s="31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="G7" s="31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="H7" s="31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="I7" s="31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="J7" s="31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="K7" s="31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="L7" s="31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="M7" s="31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>:</v>
       </c>
       <c r="N7" s="31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>;</v>
       </c>
       <c r="O7" s="31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>&lt;</v>
       </c>
       <c r="P7" s="31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>=</v>
       </c>
       <c r="Q7" s="31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>&gt;</v>
       </c>
       <c r="R7" s="32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>?</v>
       </c>
       <c r="U7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="V7" s="12"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
-      <c r="AE7" s="13"/>
-      <c r="AF7" s="13"/>
-      <c r="AG7" s="13"/>
-      <c r="AH7" s="13"/>
-      <c r="AI7" s="13"/>
-      <c r="AJ7" s="13"/>
-      <c r="AK7" s="14"/>
+      <c r="V7" s="68"/>
+      <c r="W7" s="69"/>
+      <c r="X7" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y7" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z7" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA7" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB7" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC7" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD7" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE7" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="AF7" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG7" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH7" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI7" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ7" s="69"/>
+      <c r="AK7" s="14" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="8" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="33" t="str">
-        <f t="shared" ref="C8:R8" si="4">CHAR(16*$B108 + C$103)</f>
+        <f t="shared" ref="C8:R8" si="2">CHAR(16*$B108 + C$103)</f>
         <v>@</v>
       </c>
       <c r="D8" s="34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>A</v>
       </c>
       <c r="E8" s="34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>B</v>
       </c>
       <c r="F8" s="34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>C</v>
       </c>
       <c r="G8" s="34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>D</v>
       </c>
       <c r="H8" s="34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>E</v>
       </c>
       <c r="I8" s="34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>F</v>
       </c>
       <c r="J8" s="34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>G</v>
       </c>
       <c r="K8" s="34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>H</v>
       </c>
       <c r="L8" s="34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>I</v>
       </c>
       <c r="M8" s="34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>J</v>
       </c>
       <c r="N8" s="34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>K</v>
       </c>
       <c r="O8" s="34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>L</v>
       </c>
       <c r="P8" s="34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>M</v>
       </c>
       <c r="Q8" s="34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>N</v>
       </c>
       <c r="R8" s="35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>O</v>
       </c>
       <c r="U8" s="4" t="s">
@@ -1751,15 +2061,15 @@
         <f>$C$6</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="W8" s="13"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="13"/>
-      <c r="AC8" s="13"/>
-      <c r="AD8" s="13"/>
-      <c r="AE8" s="13"/>
+      <c r="W8" s="69"/>
+      <c r="X8" s="69"/>
+      <c r="Y8" s="69"/>
+      <c r="Z8" s="69"/>
+      <c r="AA8" s="69"/>
+      <c r="AB8" s="69"/>
+      <c r="AC8" s="69"/>
+      <c r="AD8" s="69"/>
+      <c r="AE8" s="69"/>
       <c r="AF8" s="20" t="str">
         <f>$E$14</f>
         <v>¢</v>
@@ -1790,67 +2100,67 @@
         <v>21</v>
       </c>
       <c r="C9" s="33" t="str">
-        <f t="shared" ref="C9:R9" si="5">CHAR(16*$B109 + C$103)</f>
+        <f t="shared" ref="C9:R9" si="3">CHAR(16*$B109 + C$103)</f>
         <v>P</v>
       </c>
       <c r="D9" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>Q</v>
       </c>
       <c r="E9" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>R</v>
       </c>
       <c r="F9" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="G9" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>T</v>
       </c>
       <c r="H9" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>U</v>
       </c>
       <c r="I9" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>V</v>
       </c>
       <c r="J9" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>W</v>
       </c>
       <c r="K9" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>X</v>
       </c>
       <c r="L9" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>Y</v>
       </c>
       <c r="M9" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>Z</v>
       </c>
       <c r="N9" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>[</v>
       </c>
       <c r="O9" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>\</v>
       </c>
       <c r="P9" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>]</v>
       </c>
       <c r="Q9" s="34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>^</v>
       </c>
       <c r="R9" s="35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>_</v>
       </c>
       <c r="U9" s="4" t="s">
@@ -1860,15 +2170,15 @@
         <f>$I$6</f>
         <v>&amp;</v>
       </c>
-      <c r="W9" s="13"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="13"/>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="13"/>
-      <c r="AD9" s="13"/>
-      <c r="AE9" s="13"/>
+      <c r="W9" s="69"/>
+      <c r="X9" s="69"/>
+      <c r="Y9" s="69"/>
+      <c r="Z9" s="69"/>
+      <c r="AA9" s="69"/>
+      <c r="AB9" s="69"/>
+      <c r="AC9" s="69"/>
+      <c r="AD9" s="69"/>
+      <c r="AE9" s="69"/>
       <c r="AF9" s="23" t="str">
         <f>$D$6</f>
         <v>!</v>
@@ -1899,67 +2209,67 @@
         <v>22</v>
       </c>
       <c r="C10" s="36" t="str">
-        <f t="shared" ref="C10:R10" si="6">CHAR(16*$B110 + C$103)</f>
+        <f t="shared" ref="C10:R10" si="4">CHAR(16*$B110 + C$103)</f>
         <v>`</v>
       </c>
       <c r="D10" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>a</v>
       </c>
       <c r="E10" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>b</v>
       </c>
       <c r="F10" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>c</v>
       </c>
       <c r="G10" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>d</v>
       </c>
       <c r="H10" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>e</v>
       </c>
       <c r="I10" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>f</v>
       </c>
       <c r="J10" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>g</v>
       </c>
       <c r="K10" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>h</v>
       </c>
       <c r="L10" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>i</v>
       </c>
       <c r="M10" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>j</v>
       </c>
       <c r="N10" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>k</v>
       </c>
       <c r="O10" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>l</v>
       </c>
       <c r="P10" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>m</v>
       </c>
       <c r="Q10" s="37" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>n</v>
       </c>
       <c r="R10" s="38" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>o</v>
       </c>
       <c r="U10" s="4" t="s">
@@ -1973,14 +2283,14 @@
         <f>$R$6</f>
         <v>/</v>
       </c>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="13"/>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="13"/>
-      <c r="AB10" s="13"/>
-      <c r="AC10" s="13"/>
-      <c r="AD10" s="13"/>
-      <c r="AE10" s="13"/>
+      <c r="X10" s="69"/>
+      <c r="Y10" s="69"/>
+      <c r="Z10" s="69"/>
+      <c r="AA10" s="69"/>
+      <c r="AB10" s="69"/>
+      <c r="AC10" s="69"/>
+      <c r="AD10" s="69"/>
+      <c r="AE10" s="69"/>
       <c r="AF10" s="20" t="str">
         <f>$I$14</f>
         <v>¦</v>
@@ -2011,81 +2321,80 @@
         <v>23</v>
       </c>
       <c r="C11" s="36" t="str">
-        <f t="shared" ref="C11:R11" si="7">CHAR(16*$B111 + C$103)</f>
+        <f t="shared" ref="C11:R11" si="5">CHAR(16*$B111 + C$103)</f>
         <v>p</v>
       </c>
       <c r="D11" s="37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>q</v>
       </c>
       <c r="E11" s="37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>r</v>
       </c>
       <c r="F11" s="37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>s</v>
       </c>
       <c r="G11" s="37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>t</v>
       </c>
       <c r="H11" s="37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>u</v>
       </c>
       <c r="I11" s="37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>v</v>
       </c>
       <c r="J11" s="37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>w</v>
       </c>
       <c r="K11" s="37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>x</v>
       </c>
       <c r="L11" s="37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>y</v>
       </c>
       <c r="M11" s="37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>z</v>
       </c>
       <c r="N11" s="37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>{</v>
       </c>
       <c r="O11" s="37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>|</v>
       </c>
       <c r="P11" s="37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>}</v>
       </c>
       <c r="Q11" s="37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>~</v>
       </c>
-      <c r="R11" s="38" t="str">
-        <f t="shared" si="7"/>
-        <v></v>
+      <c r="R11" s="38" t="s">
+        <v>55</v>
       </c>
       <c r="U11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="V11" s="12"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="13"/>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="13"/>
-      <c r="AD11" s="13"/>
+      <c r="V11" s="68"/>
+      <c r="W11" s="69"/>
+      <c r="X11" s="69"/>
+      <c r="Y11" s="69"/>
+      <c r="Z11" s="69"/>
+      <c r="AA11" s="69"/>
+      <c r="AB11" s="69"/>
+      <c r="AC11" s="69"/>
+      <c r="AD11" s="69"/>
       <c r="AE11" s="18" t="str">
         <f>$C$10</f>
         <v>`</v>
@@ -2120,114 +2429,105 @@
         <v>24</v>
       </c>
       <c r="C12" s="39" t="str">
-        <f t="shared" ref="C12:R12" si="8">CHAR(16*$B112 + C$103)</f>
+        <f t="shared" ref="C12:R12" si="6">CHAR(16*$B112 + C$103)</f>
         <v>€</v>
       </c>
-      <c r="D12" s="40" t="str">
-        <f t="shared" si="8"/>
-        <v></v>
-      </c>
+      <c r="D12" s="65"/>
       <c r="E12" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>‚</v>
       </c>
       <c r="F12" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>ƒ</v>
       </c>
       <c r="G12" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>„</v>
       </c>
       <c r="H12" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>…</v>
       </c>
       <c r="I12" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>†</v>
       </c>
       <c r="J12" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>‡</v>
       </c>
       <c r="K12" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>ˆ</v>
       </c>
       <c r="L12" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>‰</v>
       </c>
       <c r="M12" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>Š</v>
       </c>
       <c r="N12" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>‹</v>
       </c>
       <c r="O12" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>Œ</v>
       </c>
-      <c r="P12" s="40" t="str">
-        <f t="shared" si="8"/>
-        <v></v>
-      </c>
+      <c r="P12" s="65"/>
       <c r="Q12" s="40" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>Ž</v>
       </c>
-      <c r="R12" s="41" t="str">
-        <f t="shared" si="8"/>
-        <v></v>
-      </c>
+      <c r="R12" s="64"/>
       <c r="U12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="V12" s="12"/>
+      <c r="V12" s="68"/>
       <c r="W12" s="18" t="str">
-        <f t="shared" ref="W12:AE12" si="9">D10</f>
+        <f t="shared" ref="W12:AE12" si="7">D10</f>
         <v>a</v>
       </c>
       <c r="X12" s="18" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>b</v>
       </c>
       <c r="Y12" s="18" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>c</v>
       </c>
       <c r="Z12" s="18" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>d</v>
       </c>
       <c r="AA12" s="18" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>e</v>
       </c>
       <c r="AB12" s="18" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>f</v>
       </c>
       <c r="AC12" s="18" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>g</v>
       </c>
       <c r="AD12" s="18" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>h</v>
       </c>
       <c r="AE12" s="18" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>i</v>
       </c>
-      <c r="AF12" s="13"/>
-      <c r="AG12" s="13"/>
-      <c r="AH12" s="13"/>
-      <c r="AI12" s="13"/>
-      <c r="AJ12" s="13"/>
+      <c r="AF12" s="69"/>
+      <c r="AG12" s="69"/>
+      <c r="AH12" s="69"/>
+      <c r="AI12" s="69"/>
+      <c r="AJ12" s="69"/>
       <c r="AK12" s="21" t="str">
         <f>$D$15</f>
         <v>±</v>
@@ -2237,96 +2537,92 @@
       <c r="B13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="39" t="str">
-        <f t="shared" ref="C13:R13" si="10">CHAR(16*$B113 + C$103)</f>
-        <v></v>
-      </c>
+      <c r="C13" s="66"/>
       <c r="D13" s="40" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="C13:R13" si="8">CHAR(16*$B113 + D$103)</f>
         <v>‘</v>
       </c>
       <c r="E13" s="40" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>’</v>
       </c>
       <c r="F13" s="40" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>“</v>
       </c>
       <c r="G13" s="40" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>”</v>
       </c>
       <c r="H13" s="40" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>•</v>
       </c>
       <c r="I13" s="40" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>–</v>
       </c>
       <c r="J13" s="40" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>—</v>
       </c>
       <c r="K13" s="40" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>˜</v>
       </c>
       <c r="L13" s="40" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>™</v>
       </c>
       <c r="M13" s="40" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>š</v>
       </c>
       <c r="N13" s="40" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>›</v>
       </c>
       <c r="O13" s="40" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>œ</v>
       </c>
-      <c r="P13" s="40" t="str">
-        <f t="shared" si="10"/>
-        <v></v>
+      <c r="P13" s="40" t="s">
+        <v>72</v>
       </c>
       <c r="Q13" s="40" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>ž</v>
       </c>
       <c r="R13" s="41" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>Ÿ</v>
       </c>
       <c r="U13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="V13" s="12"/>
+      <c r="V13" s="68"/>
       <c r="W13" s="18" t="str">
-        <f t="shared" ref="W13:AB13" si="11">M10</f>
+        <f t="shared" ref="W13:AB13" si="9">M10</f>
         <v>j</v>
       </c>
       <c r="X13" s="18" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>k</v>
       </c>
       <c r="Y13" s="18" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>l</v>
       </c>
       <c r="Z13" s="18" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>m</v>
       </c>
       <c r="AA13" s="18" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>n</v>
       </c>
       <c r="AB13" s="18" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>o</v>
       </c>
       <c r="AC13" s="18" t="str">
@@ -2341,194 +2637,193 @@
         <f>E11</f>
         <v>r</v>
       </c>
-      <c r="AF13" s="13"/>
-      <c r="AG13" s="13"/>
-      <c r="AH13" s="13"/>
-      <c r="AI13" s="13"/>
-      <c r="AJ13" s="13"/>
-      <c r="AK13" s="14"/>
+      <c r="AF13" s="69"/>
+      <c r="AG13" s="69"/>
+      <c r="AH13" s="69"/>
+      <c r="AI13" s="69"/>
+      <c r="AJ13" s="69"/>
+      <c r="AK13" s="70"/>
     </row>
     <row r="14" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="42" t="str">
-        <f t="shared" ref="C14:R14" si="12">CHAR(16*$B114 + C$103)</f>
-        <v> </v>
+      <c r="C14" s="42" t="s">
+        <v>87</v>
       </c>
       <c r="D14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="C14:R14" si="10">CHAR(16*$B114 + D$103)</f>
         <v>¡</v>
       </c>
       <c r="E14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>¢</v>
       </c>
       <c r="F14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>£</v>
       </c>
       <c r="G14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>¤</v>
       </c>
       <c r="H14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>¥</v>
       </c>
       <c r="I14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>¦</v>
       </c>
       <c r="J14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>§</v>
       </c>
       <c r="K14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>¨</v>
       </c>
       <c r="L14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>©</v>
       </c>
       <c r="M14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>ª</v>
       </c>
       <c r="N14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>«</v>
       </c>
       <c r="O14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>¬</v>
       </c>
       <c r="P14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>­</v>
       </c>
       <c r="Q14" s="43" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>®</v>
       </c>
       <c r="R14" s="44" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>¯</v>
       </c>
       <c r="U14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="V14" s="12"/>
+      <c r="V14" s="68"/>
       <c r="W14" s="18" t="str">
         <f>$Q$11</f>
         <v>~</v>
       </c>
       <c r="X14" s="18" t="str">
-        <f t="shared" ref="X14:AE14" si="13">F11</f>
+        <f t="shared" ref="X14:AE14" si="11">F11</f>
         <v>s</v>
       </c>
       <c r="Y14" s="18" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>t</v>
       </c>
       <c r="Z14" s="18" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>u</v>
       </c>
       <c r="AA14" s="18" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>v</v>
       </c>
       <c r="AB14" s="18" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>w</v>
       </c>
       <c r="AC14" s="18" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>x</v>
       </c>
       <c r="AD14" s="18" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>y</v>
       </c>
       <c r="AE14" s="18" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>z</v>
       </c>
-      <c r="AF14" s="13"/>
-      <c r="AG14" s="13"/>
-      <c r="AH14" s="13"/>
-      <c r="AI14" s="13"/>
-      <c r="AJ14" s="13"/>
-      <c r="AK14" s="14"/>
+      <c r="AF14" s="69"/>
+      <c r="AG14" s="69"/>
+      <c r="AH14" s="69"/>
+      <c r="AI14" s="69"/>
+      <c r="AJ14" s="69"/>
+      <c r="AK14" s="70"/>
     </row>
     <row r="15" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="42" t="str">
-        <f t="shared" ref="C15:R15" si="14">CHAR(16*$B115 + C$103)</f>
+        <f t="shared" ref="C15:R15" si="12">CHAR(16*$B115 + C$103)</f>
         <v>°</v>
       </c>
       <c r="D15" s="43" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>±</v>
       </c>
       <c r="E15" s="43" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>²</v>
       </c>
       <c r="F15" s="43" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>³</v>
       </c>
       <c r="G15" s="43" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>´</v>
       </c>
       <c r="H15" s="43" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>µ</v>
       </c>
       <c r="I15" s="43" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>¶</v>
       </c>
       <c r="J15" s="43" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>·</v>
       </c>
       <c r="K15" s="43" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>¸</v>
       </c>
       <c r="L15" s="43" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>¹</v>
       </c>
       <c r="M15" s="43" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>º</v>
       </c>
       <c r="N15" s="43" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>»</v>
       </c>
       <c r="O15" s="43" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>¼</v>
       </c>
       <c r="P15" s="43" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>½</v>
       </c>
       <c r="Q15" s="43" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>¾</v>
       </c>
       <c r="R15" s="44" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>¿</v>
       </c>
       <c r="U15" s="4" t="s">
@@ -2538,15 +2833,15 @@
         <f>$Q$9</f>
         <v>^</v>
       </c>
-      <c r="W15" s="13"/>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="13"/>
-      <c r="Z15" s="13"/>
-      <c r="AA15" s="13"/>
-      <c r="AB15" s="13"/>
-      <c r="AC15" s="13"/>
-      <c r="AD15" s="13"/>
-      <c r="AE15" s="13"/>
+      <c r="W15" s="69"/>
+      <c r="X15" s="69"/>
+      <c r="Y15" s="69"/>
+      <c r="Z15" s="69"/>
+      <c r="AA15" s="69"/>
+      <c r="AB15" s="69"/>
+      <c r="AC15" s="69"/>
+      <c r="AD15" s="69"/>
+      <c r="AE15" s="69"/>
       <c r="AF15" s="16" t="str">
         <f>$N$9</f>
         <v>[</v>
@@ -2555,77 +2850,77 @@
         <f>$P$9</f>
         <v>]</v>
       </c>
-      <c r="AH15" s="13"/>
-      <c r="AI15" s="13"/>
-      <c r="AJ15" s="13"/>
-      <c r="AK15" s="14"/>
+      <c r="AH15" s="69"/>
+      <c r="AI15" s="69"/>
+      <c r="AJ15" s="69"/>
+      <c r="AK15" s="70"/>
     </row>
     <row r="16" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="45" t="str">
-        <f t="shared" ref="C16:R16" si="15">CHAR(16*$B116 + C$103)</f>
+        <f t="shared" ref="C16:R16" si="13">CHAR(16*$B116 + C$103)</f>
         <v>À</v>
       </c>
       <c r="D16" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>Á</v>
       </c>
       <c r="E16" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>Â</v>
       </c>
       <c r="F16" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>Ã</v>
       </c>
       <c r="G16" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>Ä</v>
       </c>
       <c r="H16" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>Å</v>
       </c>
       <c r="I16" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>Æ</v>
       </c>
       <c r="J16" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>Ç</v>
       </c>
       <c r="K16" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>È</v>
       </c>
       <c r="L16" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>É</v>
       </c>
       <c r="M16" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>Ê</v>
       </c>
       <c r="N16" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>Ë</v>
       </c>
       <c r="O16" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>Ì</v>
       </c>
       <c r="P16" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>Í</v>
       </c>
       <c r="Q16" s="46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>Î</v>
       </c>
       <c r="R16" s="47" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>Ï</v>
       </c>
       <c r="U16" s="4" t="s">
@@ -2636,114 +2931,114 @@
         <v>{</v>
       </c>
       <c r="W16" s="16" t="str">
-        <f t="shared" ref="W16:AE16" si="16">D8</f>
+        <f t="shared" ref="W16:AE16" si="14">D8</f>
         <v>A</v>
       </c>
       <c r="X16" s="16" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>B</v>
       </c>
       <c r="Y16" s="16" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>C</v>
       </c>
       <c r="Z16" s="16" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>D</v>
       </c>
       <c r="AA16" s="16" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>E</v>
       </c>
       <c r="AB16" s="16" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>F</v>
       </c>
       <c r="AC16" s="16" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>G</v>
       </c>
       <c r="AD16" s="16" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>H</v>
       </c>
       <c r="AE16" s="16" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>I</v>
       </c>
-      <c r="AF16" s="13"/>
-      <c r="AG16" s="13"/>
-      <c r="AH16" s="13"/>
-      <c r="AI16" s="13"/>
-      <c r="AJ16" s="13"/>
-      <c r="AK16" s="14"/>
+      <c r="AF16" s="69"/>
+      <c r="AG16" s="69"/>
+      <c r="AH16" s="69"/>
+      <c r="AI16" s="69"/>
+      <c r="AJ16" s="69"/>
+      <c r="AK16" s="70"/>
     </row>
     <row r="17" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="45" t="str">
-        <f t="shared" ref="C17:R17" si="17">CHAR(16*$B117 + C$103)</f>
+        <f t="shared" ref="C17:R17" si="15">CHAR(16*$B117 + C$103)</f>
         <v>Ð</v>
       </c>
       <c r="D17" s="46" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Ñ</v>
       </c>
       <c r="E17" s="46" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Ò</v>
       </c>
       <c r="F17" s="46" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Ó</v>
       </c>
       <c r="G17" s="46" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Ô</v>
       </c>
       <c r="H17" s="46" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Õ</v>
       </c>
       <c r="I17" s="46" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Ö</v>
       </c>
       <c r="J17" s="46" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>×</v>
       </c>
       <c r="K17" s="46" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Ø</v>
       </c>
       <c r="L17" s="46" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Ù</v>
       </c>
       <c r="M17" s="46" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Ú</v>
       </c>
       <c r="N17" s="46" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Û</v>
       </c>
       <c r="O17" s="46" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Ü</v>
       </c>
       <c r="P17" s="46" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Ý</v>
       </c>
       <c r="Q17" s="46" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Þ</v>
       </c>
       <c r="R17" s="47" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>ß</v>
       </c>
       <c r="U17" s="4" t="s">
@@ -2754,27 +3049,27 @@
         <v>}</v>
       </c>
       <c r="W17" s="16" t="str">
-        <f t="shared" ref="W17:AB17" si="18">M8</f>
+        <f t="shared" ref="W17:AB17" si="16">M8</f>
         <v>J</v>
       </c>
       <c r="X17" s="16" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>K</v>
       </c>
       <c r="Y17" s="16" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>L</v>
       </c>
       <c r="Z17" s="16" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>M</v>
       </c>
       <c r="AA17" s="16" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>N</v>
       </c>
       <c r="AB17" s="16" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>O</v>
       </c>
       <c r="AC17" s="16" t="str">
@@ -2789,79 +3084,79 @@
         <f>E9</f>
         <v>R</v>
       </c>
-      <c r="AF17" s="13"/>
-      <c r="AG17" s="13"/>
-      <c r="AH17" s="13"/>
-      <c r="AI17" s="13"/>
-      <c r="AJ17" s="13"/>
-      <c r="AK17" s="14"/>
+      <c r="AF17" s="69"/>
+      <c r="AG17" s="69"/>
+      <c r="AH17" s="69"/>
+      <c r="AI17" s="69"/>
+      <c r="AJ17" s="69"/>
+      <c r="AK17" s="70"/>
     </row>
     <row r="18" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="48" t="str">
-        <f t="shared" ref="C18:R18" si="19">CHAR(16*$B118 + C$103)</f>
+        <f t="shared" ref="C18:R18" si="17">CHAR(16*$B118 + C$103)</f>
         <v>à</v>
       </c>
       <c r="D18" s="49" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>á</v>
       </c>
       <c r="E18" s="49" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>â</v>
       </c>
       <c r="F18" s="49" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>ã</v>
       </c>
       <c r="G18" s="49" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>ä</v>
       </c>
       <c r="H18" s="49" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>å</v>
       </c>
       <c r="I18" s="49" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>æ</v>
       </c>
       <c r="J18" s="49" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>ç</v>
       </c>
       <c r="K18" s="49" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>è</v>
       </c>
       <c r="L18" s="49" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>é</v>
       </c>
       <c r="M18" s="49" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>ê</v>
       </c>
       <c r="N18" s="49" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>ë</v>
       </c>
       <c r="O18" s="49" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>ì</v>
       </c>
       <c r="P18" s="49" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>í</v>
       </c>
       <c r="Q18" s="49" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>î</v>
       </c>
       <c r="R18" s="50" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>ï</v>
       </c>
       <c r="U18" s="4" t="s">
@@ -2871,163 +3166,165 @@
         <f>$O$9</f>
         <v>\</v>
       </c>
-      <c r="W18" s="13"/>
+      <c r="W18" s="69"/>
       <c r="X18" s="16" t="str">
-        <f t="shared" ref="X18:AE18" si="20">F9</f>
+        <f t="shared" ref="X18:AE18" si="18">F9</f>
         <v>S</v>
       </c>
       <c r="Y18" s="16" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>T</v>
       </c>
       <c r="Z18" s="16" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>U</v>
       </c>
       <c r="AA18" s="16" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>V</v>
       </c>
       <c r="AB18" s="16" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>W</v>
       </c>
       <c r="AC18" s="16" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>X</v>
       </c>
       <c r="AD18" s="16" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>Y</v>
       </c>
       <c r="AE18" s="16" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="18"/>
         <v>Z</v>
       </c>
-      <c r="AF18" s="13"/>
-      <c r="AG18" s="13"/>
-      <c r="AH18" s="13"/>
-      <c r="AI18" s="13"/>
-      <c r="AJ18" s="13"/>
-      <c r="AK18" s="14"/>
+      <c r="AF18" s="69"/>
+      <c r="AG18" s="69"/>
+      <c r="AH18" s="69"/>
+      <c r="AI18" s="69"/>
+      <c r="AJ18" s="69"/>
+      <c r="AK18" s="70"/>
     </row>
     <row r="19" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="51" t="str">
-        <f t="shared" ref="C19:R19" si="21">CHAR(16*$B119 + C$103)</f>
+        <f t="shared" ref="C19:R19" si="19">CHAR(16*$B119 + C$103)</f>
         <v>ð</v>
       </c>
       <c r="D19" s="52" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>ñ</v>
       </c>
       <c r="E19" s="52" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>ò</v>
       </c>
       <c r="F19" s="52" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>ó</v>
       </c>
       <c r="G19" s="52" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>ô</v>
       </c>
       <c r="H19" s="52" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>õ</v>
       </c>
       <c r="I19" s="52" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>ö</v>
       </c>
       <c r="J19" s="52" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>÷</v>
       </c>
       <c r="K19" s="52" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>ø</v>
       </c>
       <c r="L19" s="52" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>ù</v>
       </c>
       <c r="M19" s="52" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>ú</v>
       </c>
       <c r="N19" s="52" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>û</v>
       </c>
       <c r="O19" s="52" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>ü</v>
       </c>
       <c r="P19" s="52" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>ý</v>
       </c>
       <c r="Q19" s="52" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>þ</v>
       </c>
       <c r="R19" s="53" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>ÿ</v>
       </c>
       <c r="U19" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="V19" s="59" t="str">
-        <f t="shared" ref="V19:AE19" si="22">C7</f>
+      <c r="V19" s="58" t="str">
+        <f t="shared" ref="V19:AE19" si="20">C7</f>
         <v>0</v>
       </c>
-      <c r="W19" s="60" t="str">
-        <f t="shared" si="22"/>
+      <c r="W19" s="59" t="str">
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
-      <c r="X19" s="60" t="str">
-        <f t="shared" si="22"/>
+      <c r="X19" s="59" t="str">
+        <f t="shared" si="20"/>
         <v>2</v>
       </c>
-      <c r="Y19" s="60" t="str">
-        <f t="shared" si="22"/>
+      <c r="Y19" s="59" t="str">
+        <f t="shared" si="20"/>
         <v>3</v>
       </c>
-      <c r="Z19" s="60" t="str">
-        <f t="shared" si="22"/>
+      <c r="Z19" s="59" t="str">
+        <f t="shared" si="20"/>
         <v>4</v>
       </c>
-      <c r="AA19" s="60" t="str">
-        <f t="shared" si="22"/>
+      <c r="AA19" s="59" t="str">
+        <f t="shared" si="20"/>
         <v>5</v>
       </c>
-      <c r="AB19" s="60" t="str">
-        <f t="shared" si="22"/>
+      <c r="AB19" s="59" t="str">
+        <f t="shared" si="20"/>
         <v>6</v>
       </c>
-      <c r="AC19" s="60" t="str">
-        <f t="shared" si="22"/>
+      <c r="AC19" s="59" t="str">
+        <f t="shared" si="20"/>
         <v>7</v>
       </c>
-      <c r="AD19" s="60" t="str">
-        <f t="shared" si="22"/>
+      <c r="AD19" s="59" t="str">
+        <f t="shared" si="20"/>
         <v>8</v>
       </c>
-      <c r="AE19" s="60" t="str">
-        <f t="shared" si="22"/>
+      <c r="AE19" s="59" t="str">
+        <f t="shared" si="20"/>
         <v>9</v>
       </c>
-      <c r="AF19" s="57"/>
-      <c r="AG19" s="57"/>
-      <c r="AH19" s="57"/>
-      <c r="AI19" s="57"/>
-      <c r="AJ19" s="57"/>
-      <c r="AK19" s="58"/>
+      <c r="AF19" s="71"/>
+      <c r="AG19" s="71"/>
+      <c r="AH19" s="71"/>
+      <c r="AI19" s="71"/>
+      <c r="AJ19" s="71"/>
+      <c r="AK19" s="57" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="103" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C103" s="1">

--- a/ASIGNATURAS/SSII/TEORIA/Tablas_ASCII_Y_EBCDIC.xlsx
+++ b/ASIGNATURAS/SSII/TEORIA/Tablas_ASCII_Y_EBCDIC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CursoFP\ASIGNATURAS\SSII\TEORIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C7E43B-DC72-4BA1-A799-E705D8FF1A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9C29EA-9B72-4A00-81BC-A742EEB85E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3DD04FD7-2E28-4B73-B8DD-E110BACB8641}"/>
   </bookViews>
@@ -861,7 +861,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1043,15 +1043,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1074,6 +1065,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1406,43 +1409,43 @@
       <c r="T1" s="60"/>
     </row>
     <row r="2" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="63"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="71"/>
       <c r="U2" s="60"/>
-      <c r="V2" s="61" t="s">
+      <c r="V2" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="W2" s="62"/>
-      <c r="X2" s="62"/>
-      <c r="Y2" s="62"/>
-      <c r="Z2" s="62"/>
-      <c r="AA2" s="62"/>
-      <c r="AB2" s="62"/>
-      <c r="AC2" s="62"/>
-      <c r="AD2" s="62"/>
-      <c r="AE2" s="62"/>
-      <c r="AF2" s="62"/>
-      <c r="AG2" s="62"/>
-      <c r="AH2" s="62"/>
-      <c r="AI2" s="62"/>
-      <c r="AJ2" s="62"/>
-      <c r="AK2" s="63"/>
+      <c r="W2" s="70"/>
+      <c r="X2" s="70"/>
+      <c r="Y2" s="70"/>
+      <c r="Z2" s="70"/>
+      <c r="AA2" s="70"/>
+      <c r="AB2" s="70"/>
+      <c r="AC2" s="70"/>
+      <c r="AD2" s="70"/>
+      <c r="AE2" s="70"/>
+      <c r="AF2" s="70"/>
+      <c r="AG2" s="70"/>
+      <c r="AH2" s="70"/>
+      <c r="AI2" s="70"/>
+      <c r="AJ2" s="70"/>
+      <c r="AK2" s="71"/>
     </row>
     <row r="3" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
@@ -1620,7 +1623,7 @@
       <c r="AB4" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="AC4" s="10" t="s">
+      <c r="AC4" s="72" t="s">
         <v>55</v>
       </c>
       <c r="AD4" s="10" t="s">
@@ -1748,7 +1751,7 @@
       <c r="AJ5" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="AK5" s="67" t="s">
+      <c r="AK5" s="64" t="s">
         <v>105</v>
       </c>
     </row>
@@ -1943,8 +1946,8 @@
       <c r="U7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="V7" s="68"/>
-      <c r="W7" s="69"/>
+      <c r="V7" s="65"/>
+      <c r="W7" s="66"/>
       <c r="X7" s="13" t="s">
         <v>61</v>
       </c>
@@ -1957,7 +1960,7 @@
       <c r="AA7" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="AB7" s="13" t="s">
+      <c r="AB7" s="20" t="s">
         <v>87</v>
       </c>
       <c r="AC7" s="13" t="s">
@@ -1981,7 +1984,7 @@
       <c r="AI7" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="AJ7" s="69"/>
+      <c r="AJ7" s="66"/>
       <c r="AK7" s="14" t="s">
         <v>66</v>
       </c>
@@ -2061,15 +2064,15 @@
         <f>$C$6</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="W8" s="69"/>
-      <c r="X8" s="69"/>
-      <c r="Y8" s="69"/>
-      <c r="Z8" s="69"/>
-      <c r="AA8" s="69"/>
-      <c r="AB8" s="69"/>
-      <c r="AC8" s="69"/>
-      <c r="AD8" s="69"/>
-      <c r="AE8" s="69"/>
+      <c r="W8" s="66"/>
+      <c r="X8" s="66"/>
+      <c r="Y8" s="66"/>
+      <c r="Z8" s="66"/>
+      <c r="AA8" s="66"/>
+      <c r="AB8" s="66"/>
+      <c r="AC8" s="66"/>
+      <c r="AD8" s="66"/>
+      <c r="AE8" s="66"/>
       <c r="AF8" s="20" t="str">
         <f>$E$14</f>
         <v>¢</v>
@@ -2170,15 +2173,15 @@
         <f>$I$6</f>
         <v>&amp;</v>
       </c>
-      <c r="W9" s="69"/>
-      <c r="X9" s="69"/>
-      <c r="Y9" s="69"/>
-      <c r="Z9" s="69"/>
-      <c r="AA9" s="69"/>
-      <c r="AB9" s="69"/>
-      <c r="AC9" s="69"/>
-      <c r="AD9" s="69"/>
-      <c r="AE9" s="69"/>
+      <c r="W9" s="66"/>
+      <c r="X9" s="66"/>
+      <c r="Y9" s="66"/>
+      <c r="Z9" s="66"/>
+      <c r="AA9" s="66"/>
+      <c r="AB9" s="66"/>
+      <c r="AC9" s="66"/>
+      <c r="AD9" s="66"/>
+      <c r="AE9" s="66"/>
       <c r="AF9" s="23" t="str">
         <f>$D$6</f>
         <v>!</v>
@@ -2283,14 +2286,14 @@
         <f>$R$6</f>
         <v>/</v>
       </c>
-      <c r="X10" s="69"/>
-      <c r="Y10" s="69"/>
-      <c r="Z10" s="69"/>
-      <c r="AA10" s="69"/>
-      <c r="AB10" s="69"/>
-      <c r="AC10" s="69"/>
-      <c r="AD10" s="69"/>
-      <c r="AE10" s="69"/>
+      <c r="X10" s="66"/>
+      <c r="Y10" s="66"/>
+      <c r="Z10" s="66"/>
+      <c r="AA10" s="66"/>
+      <c r="AB10" s="66"/>
+      <c r="AC10" s="66"/>
+      <c r="AD10" s="66"/>
+      <c r="AE10" s="66"/>
       <c r="AF10" s="20" t="str">
         <f>$I$14</f>
         <v>¦</v>
@@ -2321,7 +2324,7 @@
         <v>23</v>
       </c>
       <c r="C11" s="36" t="str">
-        <f t="shared" ref="C11:R11" si="5">CHAR(16*$B111 + C$103)</f>
+        <f t="shared" ref="C11:Q11" si="5">CHAR(16*$B111 + C$103)</f>
         <v>p</v>
       </c>
       <c r="D11" s="37" t="str">
@@ -2386,15 +2389,15 @@
       <c r="U11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="V11" s="68"/>
-      <c r="W11" s="69"/>
-      <c r="X11" s="69"/>
-      <c r="Y11" s="69"/>
-      <c r="Z11" s="69"/>
-      <c r="AA11" s="69"/>
-      <c r="AB11" s="69"/>
-      <c r="AC11" s="69"/>
-      <c r="AD11" s="69"/>
+      <c r="V11" s="65"/>
+      <c r="W11" s="66"/>
+      <c r="X11" s="66"/>
+      <c r="Y11" s="66"/>
+      <c r="Z11" s="66"/>
+      <c r="AA11" s="66"/>
+      <c r="AB11" s="66"/>
+      <c r="AC11" s="66"/>
+      <c r="AD11" s="66"/>
       <c r="AE11" s="18" t="str">
         <f>$C$10</f>
         <v>`</v>
@@ -2429,10 +2432,10 @@
         <v>24</v>
       </c>
       <c r="C12" s="39" t="str">
-        <f t="shared" ref="C12:R12" si="6">CHAR(16*$B112 + C$103)</f>
+        <f t="shared" ref="C12:Q12" si="6">CHAR(16*$B112 + C$103)</f>
         <v>€</v>
       </c>
-      <c r="D12" s="65"/>
+      <c r="D12" s="62"/>
       <c r="E12" s="40" t="str">
         <f t="shared" si="6"/>
         <v>‚</v>
@@ -2477,16 +2480,16 @@
         <f t="shared" si="6"/>
         <v>Œ</v>
       </c>
-      <c r="P12" s="65"/>
+      <c r="P12" s="62"/>
       <c r="Q12" s="40" t="str">
         <f t="shared" si="6"/>
         <v>Ž</v>
       </c>
-      <c r="R12" s="64"/>
+      <c r="R12" s="61"/>
       <c r="U12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="V12" s="68"/>
+      <c r="V12" s="65"/>
       <c r="W12" s="18" t="str">
         <f t="shared" ref="W12:AE12" si="7">D10</f>
         <v>a</v>
@@ -2523,11 +2526,11 @@
         <f t="shared" si="7"/>
         <v>i</v>
       </c>
-      <c r="AF12" s="69"/>
-      <c r="AG12" s="69"/>
-      <c r="AH12" s="69"/>
-      <c r="AI12" s="69"/>
-      <c r="AJ12" s="69"/>
+      <c r="AF12" s="66"/>
+      <c r="AG12" s="66"/>
+      <c r="AH12" s="66"/>
+      <c r="AI12" s="66"/>
+      <c r="AJ12" s="66"/>
       <c r="AK12" s="21" t="str">
         <f>$D$15</f>
         <v>±</v>
@@ -2537,9 +2540,9 @@
       <c r="B13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="66"/>
+      <c r="C13" s="63"/>
       <c r="D13" s="40" t="str">
-        <f t="shared" ref="C13:R13" si="8">CHAR(16*$B113 + D$103)</f>
+        <f t="shared" ref="D13:R13" si="8">CHAR(16*$B113 + D$103)</f>
         <v>‘</v>
       </c>
       <c r="E13" s="40" t="str">
@@ -2600,7 +2603,7 @@
       <c r="U13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="V13" s="68"/>
+      <c r="V13" s="65"/>
       <c r="W13" s="18" t="str">
         <f t="shared" ref="W13:AB13" si="9">M10</f>
         <v>j</v>
@@ -2637,12 +2640,12 @@
         <f>E11</f>
         <v>r</v>
       </c>
-      <c r="AF13" s="69"/>
-      <c r="AG13" s="69"/>
-      <c r="AH13" s="69"/>
-      <c r="AI13" s="69"/>
-      <c r="AJ13" s="69"/>
-      <c r="AK13" s="70"/>
+      <c r="AF13" s="66"/>
+      <c r="AG13" s="66"/>
+      <c r="AH13" s="66"/>
+      <c r="AI13" s="66"/>
+      <c r="AJ13" s="66"/>
+      <c r="AK13" s="67"/>
     </row>
     <row r="14" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
@@ -2652,7 +2655,7 @@
         <v>87</v>
       </c>
       <c r="D14" s="43" t="str">
-        <f t="shared" ref="C14:R14" si="10">CHAR(16*$B114 + D$103)</f>
+        <f t="shared" ref="D14:R14" si="10">CHAR(16*$B114 + D$103)</f>
         <v>¡</v>
       </c>
       <c r="E14" s="43" t="str">
@@ -2714,7 +2717,7 @@
       <c r="U14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="V14" s="68"/>
+      <c r="V14" s="65"/>
       <c r="W14" s="18" t="str">
         <f>$Q$11</f>
         <v>~</v>
@@ -2751,12 +2754,12 @@
         <f t="shared" si="11"/>
         <v>z</v>
       </c>
-      <c r="AF14" s="69"/>
-      <c r="AG14" s="69"/>
-      <c r="AH14" s="69"/>
-      <c r="AI14" s="69"/>
-      <c r="AJ14" s="69"/>
-      <c r="AK14" s="70"/>
+      <c r="AF14" s="66"/>
+      <c r="AG14" s="66"/>
+      <c r="AH14" s="66"/>
+      <c r="AI14" s="66"/>
+      <c r="AJ14" s="66"/>
+      <c r="AK14" s="67"/>
     </row>
     <row r="15" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
@@ -2833,15 +2836,15 @@
         <f>$Q$9</f>
         <v>^</v>
       </c>
-      <c r="W15" s="69"/>
-      <c r="X15" s="69"/>
-      <c r="Y15" s="69"/>
-      <c r="Z15" s="69"/>
-      <c r="AA15" s="69"/>
-      <c r="AB15" s="69"/>
-      <c r="AC15" s="69"/>
-      <c r="AD15" s="69"/>
-      <c r="AE15" s="69"/>
+      <c r="W15" s="66"/>
+      <c r="X15" s="66"/>
+      <c r="Y15" s="66"/>
+      <c r="Z15" s="66"/>
+      <c r="AA15" s="66"/>
+      <c r="AB15" s="66"/>
+      <c r="AC15" s="66"/>
+      <c r="AD15" s="66"/>
+      <c r="AE15" s="66"/>
       <c r="AF15" s="16" t="str">
         <f>$N$9</f>
         <v>[</v>
@@ -2850,10 +2853,10 @@
         <f>$P$9</f>
         <v>]</v>
       </c>
-      <c r="AH15" s="69"/>
-      <c r="AI15" s="69"/>
-      <c r="AJ15" s="69"/>
-      <c r="AK15" s="70"/>
+      <c r="AH15" s="66"/>
+      <c r="AI15" s="66"/>
+      <c r="AJ15" s="66"/>
+      <c r="AK15" s="67"/>
     </row>
     <row r="16" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
@@ -2966,12 +2969,12 @@
         <f t="shared" si="14"/>
         <v>I</v>
       </c>
-      <c r="AF16" s="69"/>
-      <c r="AG16" s="69"/>
-      <c r="AH16" s="69"/>
-      <c r="AI16" s="69"/>
-      <c r="AJ16" s="69"/>
-      <c r="AK16" s="70"/>
+      <c r="AF16" s="66"/>
+      <c r="AG16" s="66"/>
+      <c r="AH16" s="66"/>
+      <c r="AI16" s="66"/>
+      <c r="AJ16" s="66"/>
+      <c r="AK16" s="67"/>
     </row>
     <row r="17" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
@@ -3084,12 +3087,12 @@
         <f>E9</f>
         <v>R</v>
       </c>
-      <c r="AF17" s="69"/>
-      <c r="AG17" s="69"/>
-      <c r="AH17" s="69"/>
-      <c r="AI17" s="69"/>
-      <c r="AJ17" s="69"/>
-      <c r="AK17" s="70"/>
+      <c r="AF17" s="66"/>
+      <c r="AG17" s="66"/>
+      <c r="AH17" s="66"/>
+      <c r="AI17" s="66"/>
+      <c r="AJ17" s="66"/>
+      <c r="AK17" s="67"/>
     </row>
     <row r="18" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
@@ -3166,7 +3169,7 @@
         <f>$O$9</f>
         <v>\</v>
       </c>
-      <c r="W18" s="69"/>
+      <c r="W18" s="66"/>
       <c r="X18" s="16" t="str">
         <f t="shared" ref="X18:AE18" si="18">F9</f>
         <v>S</v>
@@ -3199,12 +3202,12 @@
         <f t="shared" si="18"/>
         <v>Z</v>
       </c>
-      <c r="AF18" s="69"/>
-      <c r="AG18" s="69"/>
-      <c r="AH18" s="69"/>
-      <c r="AI18" s="69"/>
-      <c r="AJ18" s="69"/>
-      <c r="AK18" s="70"/>
+      <c r="AF18" s="66"/>
+      <c r="AG18" s="66"/>
+      <c r="AH18" s="66"/>
+      <c r="AI18" s="66"/>
+      <c r="AJ18" s="66"/>
+      <c r="AK18" s="67"/>
     </row>
     <row r="19" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
@@ -3317,11 +3320,11 @@
         <f t="shared" si="20"/>
         <v>9</v>
       </c>
-      <c r="AF19" s="71"/>
-      <c r="AG19" s="71"/>
-      <c r="AH19" s="71"/>
-      <c r="AI19" s="71"/>
-      <c r="AJ19" s="71"/>
+      <c r="AF19" s="68"/>
+      <c r="AG19" s="68"/>
+      <c r="AH19" s="68"/>
+      <c r="AI19" s="68"/>
+      <c r="AJ19" s="68"/>
       <c r="AK19" s="57" t="s">
         <v>101</v>
       </c>
